--- a/temp.xlsx
+++ b/temp.xlsx
@@ -11,7 +11,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+  <si>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>Top K</t>
+  </si>
+  <si>
+    <t>TP</t>
+  </si>
+  <si>
+    <t>FP</t>
+  </si>
   <si>
     <t>Total</t>
   </si>
@@ -44,11 +56,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -75,7 +91,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -422,16 +438,24 @@
   <cols>
     <col min="1" max="1" width="13.571428571428571" customWidth="1"/>
     <col min="2" max="2" width="16.571428571428573" customWidth="1"/>
-    <col min="3" max="29" width="13.571428571428571" customWidth="1"/>
+    <col min="3" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
@@ -439,30 +463,30 @@
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1">
         <v>1393</v>
@@ -485,10 +509,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1">
         <v>1436</v>
@@ -511,10 +535,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1">
         <v>23143</v>
